--- a/dataset_t6_grouped/results2/G5/G5_T2372_W0066F0003T0006Z000C1N16_analysis.xlsx
+++ b/dataset_t6_grouped/results2/G5/G5_T2372_W0066F0003T0006Z000C1N16_analysis.xlsx
@@ -480,10 +480,10 @@
         <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>35.82302795088516</v>
+        <v>5.821242042018838</v>
       </c>
       <c r="D2" t="n">
-        <v>35.78704024466211</v>
+        <v>5.815394039757593</v>
       </c>
       <c r="E2" t="n">
         <v>0</v>
